--- a/data/kz/11_rent_benchmarks.xlsx
+++ b/data/kz/11_rent_benchmarks.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>astana</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>astana</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>astana</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>astana</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>astana</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>astana</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>astana</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>AKT</t>
+          <t>aktobe</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>AKT</t>
+          <t>aktobe</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>AKT</t>
+          <t>aktobe</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>AKT</t>
+          <t>aktobe</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>AKT</t>
+          <t>aktobe</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>AKT</t>
+          <t>aktobe</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>AKT</t>
+          <t>aktobe</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>AKT</t>
+          <t>aktobe</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>AKT</t>
+          <t>aktobe</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>SHY</t>
+          <t>shymkent</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>SHY</t>
+          <t>shymkent</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>SHY</t>
+          <t>shymkent</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>SHY</t>
+          <t>shymkent</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>SHY</t>
+          <t>shymkent</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>SHY</t>
+          <t>shymkent</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>uralsk</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>uralsk</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>uralsk</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>uralsk</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>uralsk</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>uralsk</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>TAR</t>
+          <t>taraz</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>TAR</t>
+          <t>taraz</t>
         </is>
       </c>
       <c r="C49" s="14" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>TAR</t>
+          <t>taraz</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>TAR</t>
+          <t>taraz</t>
         </is>
       </c>
       <c r="C51" s="14" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>PAV</t>
+          <t>pavlodar</t>
         </is>
       </c>
       <c r="C52" s="16" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="B53" s="16" t="inlineStr">
         <is>
-          <t>PAV</t>
+          <t>pavlodar</t>
         </is>
       </c>
       <c r="C53" s="16" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>PAV</t>
+          <t>pavlodar</t>
         </is>
       </c>
       <c r="C54" s="16" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B55" s="16" t="inlineStr">
         <is>
-          <t>PAV</t>
+          <t>pavlodar</t>
         </is>
       </c>
       <c r="C55" s="16" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="B56" s="18" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>oskemen</t>
         </is>
       </c>
       <c r="C56" s="18" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="B57" s="18" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>oskemen</t>
         </is>
       </c>
       <c r="C57" s="18" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="B58" s="18" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>oskemen</t>
         </is>
       </c>
       <c r="C58" s="18" t="inlineStr">
@@ -4093,7 +4093,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4130,7 +4130,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4167,7 +4167,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4204,7 +4204,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4241,7 +4241,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4278,7 +4278,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4315,7 +4315,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4352,7 +4352,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>astana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4389,7 +4389,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>astana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4426,7 +4426,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>astana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4463,7 +4463,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>astana</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4500,7 +4500,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AKT</t>
+          <t>aktobe</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4537,7 +4537,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AKT</t>
+          <t>aktobe</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4574,7 +4574,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AKT</t>
+          <t>aktobe</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4611,7 +4611,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AKT</t>
+          <t>aktobe</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4648,7 +4648,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AKT</t>
+          <t>aktobe</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4685,7 +4685,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SHY</t>
+          <t>shymkent</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4722,7 +4722,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SHY</t>
+          <t>shymkent</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4759,7 +4759,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SHY</t>
+          <t>shymkent</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4796,7 +4796,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SHY</t>
+          <t>shymkent</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4833,7 +4833,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>uralsk</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4870,7 +4870,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>uralsk</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4907,7 +4907,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>uralsk</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4944,7 +4944,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>uralsk</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4981,7 +4981,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TAR</t>
+          <t>taraz</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5018,7 +5018,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TAR</t>
+          <t>taraz</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5055,7 +5055,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PAV</t>
+          <t>pavlodar</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5092,7 +5092,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PAV</t>
+          <t>pavlodar</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5129,7 +5129,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>oskemen</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5166,7 +5166,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>oskemen</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
